--- a/official-result/tables/translation/translation-result.xlsx
+++ b/official-result/tables/translation/translation-result.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Multiagent Research\ProjectEvalPlus\official-result\translation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30458A02-7128-4F1E-8300-C8CF42EAAC89}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6B6DAF48-0CC2-4E72-AEE0-7F95837CCAC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="14790" xr2:uid="{E68E839D-6AA9-486A-BDCC-9ED3AF3535B8}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{E68E839D-6AA9-486A-BDCC-9ED3AF3535B8}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="2" r:id="rId1"/>
@@ -18,9 +18,21 @@
     <sheet name="GPT-5-Mini" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -142,9 +154,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 主题">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -182,7 +194,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -288,7 +300,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -430,7 +442,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -602,7 +614,7 @@
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
       <c r="G3" s="3">
-        <f>MAX(B3:F3)</f>
+        <f t="shared" ref="G3:G22" si="0">MAX(B3:F3)</f>
         <v>0.90909090909090895</v>
       </c>
       <c r="J3" s="5">
@@ -648,7 +660,7 @@
         <v>0.77777777777777701</v>
       </c>
       <c r="G4" s="3">
-        <f>MAX(B4:F4)</f>
+        <f t="shared" si="0"/>
         <v>0.77777777777777701</v>
       </c>
       <c r="J4" s="5">
@@ -670,7 +682,7 @@
         <v>4</v>
       </c>
       <c r="P4" s="3">
-        <f t="shared" ref="P4:P22" si="0">MAX(K4:O4)</f>
+        <f t="shared" ref="P4:P22" si="1">MAX(K4:O4)</f>
         <v>1</v>
       </c>
     </row>
@@ -694,7 +706,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="3">
-        <f>MAX(B5:F5)</f>
+        <f t="shared" si="0"/>
         <v>0.625</v>
       </c>
       <c r="J5" s="5">
@@ -716,7 +728,7 @@
         <v>4</v>
       </c>
       <c r="P5" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.9375</v>
       </c>
     </row>
@@ -738,7 +750,7 @@
       </c>
       <c r="F6" s="3"/>
       <c r="G6" s="3">
-        <f>MAX(B6:F6)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="J6" s="5">
@@ -760,7 +772,7 @@
         <v>4</v>
       </c>
       <c r="P6" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.94117647058823495</v>
       </c>
     </row>
@@ -778,7 +790,7 @@
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
       <c r="G7" s="3">
-        <f>MAX(B7:F7)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="J7" s="5">
@@ -800,7 +812,7 @@
         <v>4</v>
       </c>
       <c r="P7" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -824,7 +836,7 @@
         <v>0</v>
       </c>
       <c r="G8" s="3">
-        <f>MAX(B8:F8)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J8" s="5">
@@ -846,7 +858,7 @@
         <v>4</v>
       </c>
       <c r="P8" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -870,7 +882,7 @@
         <v>0</v>
       </c>
       <c r="G9" s="3">
-        <f>MAX(B9:F9)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J9" s="5">
@@ -892,7 +904,7 @@
         <v>0.625</v>
       </c>
       <c r="P9" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.625</v>
       </c>
     </row>
@@ -916,7 +928,7 @@
         <v>5.5555555555555497E-2</v>
       </c>
       <c r="G10" s="3">
-        <f>MAX(B10:F10)</f>
+        <f t="shared" si="0"/>
         <v>5.5555555555555497E-2</v>
       </c>
       <c r="J10" s="5">
@@ -938,7 +950,7 @@
         <v>4</v>
       </c>
       <c r="P10" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -960,7 +972,7 @@
       </c>
       <c r="F11" s="3"/>
       <c r="G11" s="3">
-        <f>MAX(B11:F11)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="J11" s="5">
@@ -982,7 +994,7 @@
         <v>4</v>
       </c>
       <c r="P11" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -1006,7 +1018,7 @@
         <v>0</v>
       </c>
       <c r="G12" s="3">
-        <f>MAX(B12:F12)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J12" s="5">
@@ -1028,7 +1040,7 @@
         <v>4</v>
       </c>
       <c r="P12" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.90476190476190399</v>
       </c>
     </row>
@@ -1052,7 +1064,7 @@
         <v>0.25</v>
       </c>
       <c r="G13" s="3">
-        <f>MAX(B13:F13)</f>
+        <f t="shared" si="0"/>
         <v>0.25</v>
       </c>
       <c r="J13" s="5">
@@ -1074,7 +1086,7 @@
         <v>0.875</v>
       </c>
       <c r="P13" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.875</v>
       </c>
     </row>
@@ -1098,7 +1110,7 @@
         <v>0</v>
       </c>
       <c r="G14" s="3">
-        <f>MAX(B14:F14)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J14" s="5">
@@ -1120,7 +1132,7 @@
         <v>0.5</v>
       </c>
       <c r="P14" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.5</v>
       </c>
     </row>
@@ -1144,7 +1156,7 @@
         <v>0</v>
       </c>
       <c r="G15" s="3">
-        <f>MAX(B15:F15)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J15" s="5">
@@ -1166,7 +1178,7 @@
         <v>0.88</v>
       </c>
       <c r="P15" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.88</v>
       </c>
     </row>
@@ -1182,7 +1194,7 @@
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
       <c r="G16" s="3">
-        <f>MAX(B16:F16)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="J16" s="5">
@@ -1204,7 +1216,7 @@
         <v>4</v>
       </c>
       <c r="P16" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -1220,7 +1232,7 @@
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
       <c r="G17" s="3">
-        <f>MAX(B17:F17)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="J17" s="5">
@@ -1242,7 +1254,7 @@
         <v>4</v>
       </c>
       <c r="P17" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -1266,7 +1278,7 @@
         <v>0.33333333333333298</v>
       </c>
       <c r="G18" s="3">
-        <f>MAX(B18:F18)</f>
+        <f t="shared" si="0"/>
         <v>0.33333333333333298</v>
       </c>
       <c r="J18" s="5">
@@ -1288,7 +1300,7 @@
         <v>0.33333333333333298</v>
       </c>
       <c r="P18" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.33333333333333298</v>
       </c>
     </row>
@@ -1312,7 +1324,7 @@
         <v>0.33333333333333298</v>
       </c>
       <c r="G19" s="3">
-        <f>MAX(B19:F19)</f>
+        <f t="shared" si="0"/>
         <v>0.33333333333333298</v>
       </c>
       <c r="J19" s="5">
@@ -1334,7 +1346,7 @@
         <v>0.5</v>
       </c>
       <c r="P19" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.66666666666666596</v>
       </c>
     </row>
@@ -1358,7 +1370,7 @@
         <v>7.1428571428571397E-2</v>
       </c>
       <c r="G20" s="3">
-        <f>MAX(B20:F20)</f>
+        <f t="shared" si="0"/>
         <v>7.1428571428571397E-2</v>
       </c>
       <c r="J20" s="5">
@@ -1380,7 +1392,7 @@
         <v>1</v>
       </c>
       <c r="P20" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -1404,7 +1416,7 @@
         <v>0</v>
       </c>
       <c r="G21" s="3">
-        <f>MAX(B21:F21)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J21" s="5">
@@ -1426,7 +1438,7 @@
         <v>0.5</v>
       </c>
       <c r="P21" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.5</v>
       </c>
     </row>
@@ -1450,7 +1462,7 @@
         <v>0</v>
       </c>
       <c r="G22" s="3">
-        <f>MAX(B22:F22)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J22" s="5">
@@ -1472,7 +1484,7 @@
         <v>7.69230769230769E-2</v>
       </c>
       <c r="P22" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>7.69230769230769E-2</v>
       </c>
     </row>
@@ -1737,7 +1749,10 @@
   <dimension ref="A1:P23"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
+    <col min="1" max="1" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.75" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="36.08203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1815,7 +1830,7 @@
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
       <c r="G3" s="3">
-        <f>MAX(B3:F3)</f>
+        <f t="shared" ref="G3:G22" si="0">MAX(B3:F3)</f>
         <v>1</v>
       </c>
       <c r="J3" s="5">
@@ -1849,7 +1864,7 @@
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
       <c r="G4" s="3">
-        <f>MAX(B4:F4)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="J4" s="5">
@@ -1863,7 +1878,7 @@
       <c r="N4" s="4"/>
       <c r="O4" s="4"/>
       <c r="P4" s="3">
-        <f t="shared" ref="P4:P22" si="0">MAX(K4:O4)</f>
+        <f t="shared" ref="P4:P22" si="1">MAX(K4:O4)</f>
         <v>1</v>
       </c>
     </row>
@@ -1879,7 +1894,7 @@
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
       <c r="G5" s="3">
-        <f>MAX(B5:F5)</f>
+        <f t="shared" si="0"/>
         <v>0.9375</v>
       </c>
       <c r="H5">
@@ -1896,7 +1911,7 @@
       <c r="N5" s="4"/>
       <c r="O5" s="4"/>
       <c r="P5" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -1916,7 +1931,7 @@
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
       <c r="G6" s="3">
-        <f>MAX(B6:F6)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="J6" s="5">
@@ -1932,7 +1947,7 @@
       <c r="N6" s="4"/>
       <c r="O6" s="4"/>
       <c r="P6" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -1954,7 +1969,7 @@
       </c>
       <c r="F7" s="3"/>
       <c r="G7" s="3">
-        <f>MAX(B7:F7)</f>
+        <f t="shared" si="0"/>
         <v>0.92307692307692302</v>
       </c>
       <c r="H7">
@@ -1973,7 +1988,7 @@
       <c r="N7" s="4"/>
       <c r="O7" s="4"/>
       <c r="P7" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -1993,7 +2008,7 @@
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
       <c r="G8" s="3">
-        <f>MAX(B8:F8)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="J8" s="5">
@@ -2009,7 +2024,7 @@
       <c r="N8" s="4"/>
       <c r="O8" s="4"/>
       <c r="P8" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -2033,7 +2048,7 @@
         <v>0.83333333333333304</v>
       </c>
       <c r="G9" s="3">
-        <f>MAX(B9:F9)</f>
+        <f t="shared" si="0"/>
         <v>0.83333333333333304</v>
       </c>
       <c r="H9">
@@ -2052,7 +2067,7 @@
       <c r="N9" s="4"/>
       <c r="O9" s="4"/>
       <c r="P9" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -2076,7 +2091,7 @@
         <v>0.72222222222222199</v>
       </c>
       <c r="G10" s="3">
-        <f>MAX(B10:F10)</f>
+        <f t="shared" si="0"/>
         <v>0.72222222222222199</v>
       </c>
       <c r="H10">
@@ -2093,7 +2108,7 @@
       <c r="N10" s="4"/>
       <c r="O10" s="4"/>
       <c r="P10" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -2109,7 +2124,7 @@
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
       <c r="G11" s="3">
-        <f>MAX(B11:F11)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="J11" s="5">
@@ -2123,7 +2138,7 @@
       <c r="N11" s="4"/>
       <c r="O11" s="4"/>
       <c r="P11" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -2147,7 +2162,7 @@
         <v>0.76190476190476097</v>
       </c>
       <c r="G12" s="3">
-        <f>MAX(B12:F12)</f>
+        <f t="shared" si="0"/>
         <v>0.76190476190476097</v>
       </c>
       <c r="H12">
@@ -2164,7 +2179,7 @@
       <c r="N12" s="4"/>
       <c r="O12" s="4"/>
       <c r="P12" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -2188,7 +2203,7 @@
         <v>0.5</v>
       </c>
       <c r="G13" s="3">
-        <f>MAX(B13:F13)</f>
+        <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
       <c r="J13" s="5">
@@ -2210,7 +2225,7 @@
         <v>1</v>
       </c>
       <c r="P13" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -2234,7 +2249,7 @@
         <v>0.72222222222222199</v>
       </c>
       <c r="G14" s="3">
-        <f>MAX(B14:F14)</f>
+        <f t="shared" si="0"/>
         <v>0.72222222222222199</v>
       </c>
       <c r="H14">
@@ -2259,7 +2274,7 @@
         <v>0.77777777777777701</v>
       </c>
       <c r="P14" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.77777777777777701</v>
       </c>
     </row>
@@ -2283,7 +2298,7 @@
         <v>0</v>
       </c>
       <c r="G15" s="3">
-        <f>MAX(B15:F15)</f>
+        <f t="shared" si="0"/>
         <v>0.64</v>
       </c>
       <c r="H15">
@@ -2308,7 +2323,7 @@
         <v>0.4</v>
       </c>
       <c r="P15" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.4</v>
       </c>
     </row>
@@ -2324,7 +2339,7 @@
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
       <c r="G16" s="3">
-        <f>MAX(B16:F16)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="J16" s="5">
@@ -2338,7 +2353,7 @@
       <c r="N16" s="4"/>
       <c r="O16" s="4"/>
       <c r="P16" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -2354,7 +2369,7 @@
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
       <c r="G17" s="3">
-        <f>MAX(B17:F17)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="J17" s="5">
@@ -2368,7 +2383,7 @@
       <c r="N17" s="4"/>
       <c r="O17" s="4"/>
       <c r="P17" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -2380,7 +2395,7 @@
         <v>1</v>
       </c>
       <c r="G18" s="3">
-        <f>MAX(B18:F18)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="H18">
@@ -2397,7 +2412,7 @@
       <c r="N18" s="4"/>
       <c r="O18" s="4"/>
       <c r="P18" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -2413,7 +2428,7 @@
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
       <c r="G19" s="3">
-        <f>MAX(B19:F19)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="J19" s="5">
@@ -2433,7 +2448,7 @@
       </c>
       <c r="O19" s="4"/>
       <c r="P19" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -2444,20 +2459,12 @@
       <c r="B20" s="3">
         <v>1</v>
       </c>
-      <c r="C20" s="3">
-        <v>1</v>
-      </c>
-      <c r="D20" s="3">
-        <v>1</v>
-      </c>
-      <c r="E20" s="3">
-        <v>1</v>
-      </c>
-      <c r="F20" s="3">
-        <v>1</v>
-      </c>
+      <c r="C20" s="3"/>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
       <c r="G20" s="3">
-        <f>MAX(B20:F20)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="H20">
@@ -2474,7 +2481,7 @@
       <c r="N20" s="6"/>
       <c r="O20" s="6"/>
       <c r="P20" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -2498,7 +2505,7 @@
         <v>0.125</v>
       </c>
       <c r="G21" s="3">
-        <f>MAX(B21:F21)</f>
+        <f t="shared" si="0"/>
         <v>0.625</v>
       </c>
       <c r="H21" t="s">
@@ -2523,7 +2530,7 @@
         <v>0.75</v>
       </c>
       <c r="P21" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.875</v>
       </c>
     </row>
@@ -2547,7 +2554,7 @@
         <v>0.57692307692307598</v>
       </c>
       <c r="G22" s="3">
-        <f>MAX(B22:F22)</f>
+        <f t="shared" si="0"/>
         <v>0.57692307692307598</v>
       </c>
       <c r="H22">
@@ -2572,7 +2579,7 @@
         <v>0.61538461538461497</v>
       </c>
       <c r="P22" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.61538461538461497</v>
       </c>
     </row>
